--- a/players.xlsx
+++ b/players.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,15 @@
           <t>starrings</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>July2025_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>671119</t>
-        </is>
+      <c r="A2" t="n">
+        <v>671119</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -479,12 +482,13 @@
       <c r="E2" t="n">
         <v>2.1</v>
       </c>
+      <c r="F2" t="n">
+        <v>497</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>327350</t>
-        </is>
+      <c r="A3" t="n">
+        <v>327350</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -504,12 +508,13 @@
       <c r="E3" t="n">
         <v>2.1</v>
       </c>
+      <c r="F3" t="n">
+        <v>682</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>547834</t>
-        </is>
+      <c r="A4" t="n">
+        <v>547834</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -529,12 +534,13 @@
       <c r="E4" t="n">
         <v>2.1</v>
       </c>
+      <c r="F4" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>74333</t>
-        </is>
+      <c r="A5" t="n">
+        <v>74333</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -554,12 +560,13 @@
       <c r="E5" t="n">
         <v>1.1</v>
       </c>
+      <c r="F5" t="n">
+        <v>1314</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>534286</t>
-        </is>
+      <c r="A6" t="n">
+        <v>534286</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -579,12 +586,13 @@
       <c r="E6" t="n">
         <v>2.2</v>
       </c>
+      <c r="F6" t="n">
+        <v>453</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>548731</t>
-        </is>
+      <c r="A7" t="n">
+        <v>548731</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -604,12 +612,13 @@
       <c r="E7" t="n">
         <v>2.2</v>
       </c>
+      <c r="F7" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>110556</t>
-        </is>
+      <c r="A8" t="n">
+        <v>110556</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -629,12 +638,13 @@
       <c r="E8" t="n">
         <v>1.2</v>
       </c>
+      <c r="F8" t="n">
+        <v>643</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>662721</t>
-        </is>
+      <c r="A9" t="n">
+        <v>662721</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -654,12 +664,13 @@
       <c r="E9" t="n">
         <v>3.1</v>
       </c>
+      <c r="F9" t="n">
+        <v>516</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3389399</t>
-        </is>
+      <c r="A10" t="n">
+        <v>3389399</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -679,12 +690,13 @@
       <c r="E10" t="n">
         <v>1.2</v>
       </c>
+      <c r="F10" t="n">
+        <v>695</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>74309</t>
-        </is>
+      <c r="A11" t="n">
+        <v>74309</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -704,12 +716,13 @@
       <c r="E11" t="n">
         <v>2.2</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>689814</t>
-        </is>
+      <c r="A12" t="n">
+        <v>689814</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -729,12 +742,13 @@
       <c r="E12" t="n">
         <v>3.1</v>
       </c>
+      <c r="F12" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>882252</t>
-        </is>
+      <c r="A13" t="n">
+        <v>882252</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -754,12 +768,13 @@
       <c r="E13" t="n">
         <v>2.2</v>
       </c>
+      <c r="F13" t="n">
+        <v>321</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>893163</t>
-        </is>
+      <c r="A14" t="n">
+        <v>893163</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -779,12 +794,13 @@
       <c r="E14" t="n">
         <v>3.1</v>
       </c>
+      <c r="F14" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3465549</t>
-        </is>
+      <c r="A15" t="n">
+        <v>3465549</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -804,12 +820,13 @@
       <c r="E15" t="n">
         <v>4</v>
       </c>
+      <c r="F15" t="n">
+        <v>1634</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>104625</t>
-        </is>
+      <c r="A16" t="n">
+        <v>104625</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -829,12 +846,13 @@
       <c r="E16" t="n">
         <v>1.2</v>
       </c>
+      <c r="F16" t="n">
+        <v>176</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>74263</t>
-        </is>
+      <c r="A17" t="n">
+        <v>74263</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -854,12 +872,13 @@
       <c r="E17" t="n">
         <v>2.1</v>
       </c>
+      <c r="F17" t="n">
+        <v>605</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>91224</t>
-        </is>
+      <c r="A18" t="n">
+        <v>91224</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -879,12 +898,13 @@
       <c r="E18" t="n">
         <v>1.2</v>
       </c>
+      <c r="F18" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>661554</t>
-        </is>
+      <c r="A19" t="n">
+        <v>661554</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -904,12 +924,13 @@
       <c r="E19" t="n">
         <v>3.1</v>
       </c>
+      <c r="F19" t="n">
+        <v>343</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>74266</t>
-        </is>
+      <c r="A20" t="n">
+        <v>74266</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -929,12 +950,13 @@
       <c r="E20" t="n">
         <v>2.1</v>
       </c>
+      <c r="F20" t="n">
+        <v>362</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>74331</t>
-        </is>
+      <c r="A21" t="n">
+        <v>74331</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -954,12 +976,13 @@
       <c r="E21" t="n">
         <v>1.2</v>
       </c>
+      <c r="F21" t="n">
+        <v>266</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>76413</t>
-        </is>
+      <c r="A22" t="n">
+        <v>76413</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -979,12 +1002,13 @@
       <c r="E22" t="n">
         <v>1.1</v>
       </c>
+      <c r="F22" t="n">
+        <v>440</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>74332</t>
-        </is>
+      <c r="A23" t="n">
+        <v>74332</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1004,12 +1028,13 @@
       <c r="E23" t="n">
         <v>2.2</v>
       </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>89687</t>
-        </is>
+      <c r="A24" t="n">
+        <v>89687</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1029,12 +1054,13 @@
       <c r="E24" t="n">
         <v>4</v>
       </c>
+      <c r="F24" t="n">
+        <v>672</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>327209</t>
-        </is>
+      <c r="A25" t="n">
+        <v>327209</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1054,12 +1080,13 @@
       <c r="E25" t="n">
         <v>3.1</v>
       </c>
+      <c r="F25" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>882428</t>
-        </is>
+      <c r="A26" t="n">
+        <v>882428</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1079,12 +1106,13 @@
       <c r="E26" t="n">
         <v>3.2</v>
       </c>
+      <c r="F26" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>76411</t>
-        </is>
+      <c r="A27" t="n">
+        <v>76411</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1104,12 +1132,13 @@
       <c r="E27" t="n">
         <v>1.1</v>
       </c>
+      <c r="F27" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>74274</t>
-        </is>
+      <c r="A28" t="n">
+        <v>74274</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1129,12 +1158,13 @@
       <c r="E28" t="n">
         <v>1.1</v>
       </c>
+      <c r="F28" t="n">
+        <v>476</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>683544</t>
-        </is>
+      <c r="A29" t="n">
+        <v>683544</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1154,12 +1184,13 @@
       <c r="E29" t="n">
         <v>4</v>
       </c>
+      <c r="F29" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>3281758</t>
-        </is>
+      <c r="A30" t="n">
+        <v>3281758</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1179,12 +1210,13 @@
       <c r="E30" t="n">
         <v>4</v>
       </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>74281</t>
-        </is>
+      <c r="A31" t="n">
+        <v>74281</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1204,12 +1236,13 @@
       <c r="E31" t="n">
         <v>1.1</v>
       </c>
+      <c r="F31" t="n">
+        <v>521</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>3276978</t>
-        </is>
+      <c r="A32" t="n">
+        <v>3276978</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1229,12 +1262,13 @@
       <c r="E32" t="n">
         <v>4</v>
       </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>76412</t>
-        </is>
+      <c r="A33" t="n">
+        <v>76412</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1254,12 +1288,13 @@
       <c r="E33" t="n">
         <v>4</v>
       </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>687333</t>
-        </is>
+      <c r="A34" t="n">
+        <v>687333</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1279,12 +1314,13 @@
       <c r="E34" t="n">
         <v>4</v>
       </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>326899</t>
-        </is>
+      <c r="A35" t="n">
+        <v>326899</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1304,12 +1340,13 @@
       <c r="E35" t="n">
         <v>3.2</v>
       </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>3468653</t>
-        </is>
+      <c r="A36" t="n">
+        <v>3468653</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1329,12 +1366,13 @@
       <c r="E36" t="n">
         <v>4</v>
       </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>75760</t>
-        </is>
+      <c r="A37" t="n">
+        <v>75760</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1354,12 +1392,13 @@
       <c r="E37" t="n">
         <v>2.1</v>
       </c>
+      <c r="F37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>74265</t>
-        </is>
+      <c r="A38" t="n">
+        <v>74265</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1379,12 +1418,13 @@
       <c r="E38" t="n">
         <v>4</v>
       </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>554268</t>
-        </is>
+      <c r="A39" t="n">
+        <v>554268</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1404,12 +1444,13 @@
       <c r="E39" t="n">
         <v>4</v>
       </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>3281295</t>
-        </is>
+      <c r="A40" t="n">
+        <v>3281295</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1429,12 +1470,13 @@
       <c r="E40" t="n">
         <v>3.2</v>
       </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>327187</t>
-        </is>
+      <c r="A41" t="n">
+        <v>327187</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1454,12 +1496,13 @@
       <c r="E41" t="n">
         <v>4</v>
       </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>103786</t>
-        </is>
+      <c r="A42" t="n">
+        <v>103786</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1479,12 +1522,13 @@
       <c r="E42" t="n">
         <v>4</v>
       </c>
+      <c r="F42" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>3468321</t>
-        </is>
+      <c r="A43" t="n">
+        <v>3468321</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1504,12 +1548,13 @@
       <c r="E43" t="n">
         <v>4</v>
       </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>683019</t>
-        </is>
+      <c r="A44" t="n">
+        <v>683019</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1528,6 +1573,9 @@
       </c>
       <c r="E44" t="n">
         <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/players.xlsx
+++ b/players.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,16 @@
           <t>July2025_score</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>August2025_score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>May2025_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -485,6 +495,12 @@
       <c r="F2" t="n">
         <v>497</v>
       </c>
+      <c r="G2" t="n">
+        <v>497</v>
+      </c>
+      <c r="H2" t="n">
+        <v>497</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -511,6 +527,12 @@
       <c r="F3" t="n">
         <v>682</v>
       </c>
+      <c r="G3" t="n">
+        <v>682</v>
+      </c>
+      <c r="H3" t="n">
+        <v>682</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -537,6 +559,12 @@
       <c r="F4" t="n">
         <v>833</v>
       </c>
+      <c r="G4" t="n">
+        <v>833</v>
+      </c>
+      <c r="H4" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -563,6 +591,12 @@
       <c r="F5" t="n">
         <v>1314</v>
       </c>
+      <c r="G5" t="n">
+        <v>1314</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1314</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -589,6 +623,12 @@
       <c r="F6" t="n">
         <v>453</v>
       </c>
+      <c r="G6" t="n">
+        <v>453</v>
+      </c>
+      <c r="H6" t="n">
+        <v>453</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -615,6 +655,12 @@
       <c r="F7" t="n">
         <v>339</v>
       </c>
+      <c r="G7" t="n">
+        <v>339</v>
+      </c>
+      <c r="H7" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -641,6 +687,12 @@
       <c r="F8" t="n">
         <v>643</v>
       </c>
+      <c r="G8" t="n">
+        <v>643</v>
+      </c>
+      <c r="H8" t="n">
+        <v>643</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -667,6 +719,12 @@
       <c r="F9" t="n">
         <v>516</v>
       </c>
+      <c r="G9" t="n">
+        <v>516</v>
+      </c>
+      <c r="H9" t="n">
+        <v>516</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -693,6 +751,12 @@
       <c r="F10" t="n">
         <v>695</v>
       </c>
+      <c r="G10" t="n">
+        <v>695</v>
+      </c>
+      <c r="H10" t="n">
+        <v>695</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -719,6 +783,12 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -745,6 +815,12 @@
       <c r="F12" t="n">
         <v>153</v>
       </c>
+      <c r="G12" t="n">
+        <v>153</v>
+      </c>
+      <c r="H12" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -771,6 +847,12 @@
       <c r="F13" t="n">
         <v>321</v>
       </c>
+      <c r="G13" t="n">
+        <v>321</v>
+      </c>
+      <c r="H13" t="n">
+        <v>321</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -797,6 +879,12 @@
       <c r="F14" t="n">
         <v>147</v>
       </c>
+      <c r="G14" t="n">
+        <v>147</v>
+      </c>
+      <c r="H14" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -823,6 +911,12 @@
       <c r="F15" t="n">
         <v>1634</v>
       </c>
+      <c r="G15" t="n">
+        <v>1634</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1634</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -849,6 +943,12 @@
       <c r="F16" t="n">
         <v>176</v>
       </c>
+      <c r="G16" t="n">
+        <v>176</v>
+      </c>
+      <c r="H16" t="n">
+        <v>176</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -875,6 +975,12 @@
       <c r="F17" t="n">
         <v>605</v>
       </c>
+      <c r="G17" t="n">
+        <v>605</v>
+      </c>
+      <c r="H17" t="n">
+        <v>605</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -901,6 +1007,12 @@
       <c r="F18" t="n">
         <v>429</v>
       </c>
+      <c r="G18" t="n">
+        <v>429</v>
+      </c>
+      <c r="H18" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -927,6 +1039,12 @@
       <c r="F19" t="n">
         <v>343</v>
       </c>
+      <c r="G19" t="n">
+        <v>343</v>
+      </c>
+      <c r="H19" t="n">
+        <v>343</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -953,6 +1071,12 @@
       <c r="F20" t="n">
         <v>362</v>
       </c>
+      <c r="G20" t="n">
+        <v>362</v>
+      </c>
+      <c r="H20" t="n">
+        <v>362</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -979,6 +1103,12 @@
       <c r="F21" t="n">
         <v>266</v>
       </c>
+      <c r="G21" t="n">
+        <v>266</v>
+      </c>
+      <c r="H21" t="n">
+        <v>266</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1005,6 +1135,12 @@
       <c r="F22" t="n">
         <v>440</v>
       </c>
+      <c r="G22" t="n">
+        <v>440</v>
+      </c>
+      <c r="H22" t="n">
+        <v>440</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1031,6 +1167,12 @@
       <c r="F23" t="n">
         <v>0</v>
       </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1057,6 +1199,12 @@
       <c r="F24" t="n">
         <v>672</v>
       </c>
+      <c r="G24" t="n">
+        <v>672</v>
+      </c>
+      <c r="H24" t="n">
+        <v>672</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1083,6 +1231,12 @@
       <c r="F25" t="n">
         <v>73</v>
       </c>
+      <c r="G25" t="n">
+        <v>73</v>
+      </c>
+      <c r="H25" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1109,6 +1263,12 @@
       <c r="F26" t="n">
         <v>59</v>
       </c>
+      <c r="G26" t="n">
+        <v>59</v>
+      </c>
+      <c r="H26" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1135,6 +1295,12 @@
       <c r="F27" t="n">
         <v>385</v>
       </c>
+      <c r="G27" t="n">
+        <v>385</v>
+      </c>
+      <c r="H27" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1161,6 +1327,12 @@
       <c r="F28" t="n">
         <v>476</v>
       </c>
+      <c r="G28" t="n">
+        <v>476</v>
+      </c>
+      <c r="H28" t="n">
+        <v>476</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1187,6 +1359,12 @@
       <c r="F29" t="n">
         <v>30</v>
       </c>
+      <c r="G29" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1213,6 +1391,12 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1239,6 +1423,12 @@
       <c r="F31" t="n">
         <v>521</v>
       </c>
+      <c r="G31" t="n">
+        <v>521</v>
+      </c>
+      <c r="H31" t="n">
+        <v>521</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1265,6 +1455,12 @@
       <c r="F32" t="n">
         <v>0</v>
       </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1291,6 +1487,12 @@
       <c r="F33" t="n">
         <v>0</v>
       </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1317,6 +1519,12 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1343,6 +1551,12 @@
       <c r="F35" t="n">
         <v>0</v>
       </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1369,6 +1583,12 @@
       <c r="F36" t="n">
         <v>0</v>
       </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1395,6 +1615,12 @@
       <c r="F37" t="n">
         <v>7</v>
       </c>
+      <c r="G37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1421,6 +1647,12 @@
       <c r="F38" t="n">
         <v>6</v>
       </c>
+      <c r="G38" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1447,6 +1679,12 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1473,6 +1711,12 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1499,6 +1743,12 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1525,6 +1775,12 @@
       <c r="F42" t="n">
         <v>10</v>
       </c>
+      <c r="G42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1551,6 +1807,12 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1575,6 +1837,12 @@
         <v>4</v>
       </c>
       <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/players.xlsx
+++ b/players.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>May2025_score</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>June2025_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -499,6 +504,9 @@
         <v>497</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>497</v>
       </c>
     </row>
@@ -533,6 +541,9 @@
       <c r="H3" t="n">
         <v>682</v>
       </c>
+      <c r="I3" t="n">
+        <v>682</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -565,6 +576,9 @@
       <c r="H4" t="n">
         <v>833</v>
       </c>
+      <c r="I4" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -595,7 +609,10 @@
         <v>1314</v>
       </c>
       <c r="H5" t="n">
-        <v>1314</v>
+        <v>1971</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1971</v>
       </c>
     </row>
     <row r="6">
@@ -629,6 +646,9 @@
       <c r="H6" t="n">
         <v>453</v>
       </c>
+      <c r="I6" t="n">
+        <v>453</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -661,6 +681,9 @@
       <c r="H7" t="n">
         <v>339</v>
       </c>
+      <c r="I7" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,6 +716,9 @@
       <c r="H8" t="n">
         <v>643</v>
       </c>
+      <c r="I8" t="n">
+        <v>643</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -725,6 +751,9 @@
       <c r="H9" t="n">
         <v>516</v>
       </c>
+      <c r="I9" t="n">
+        <v>516</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -757,6 +786,9 @@
       <c r="H10" t="n">
         <v>695</v>
       </c>
+      <c r="I10" t="n">
+        <v>695</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -789,6 +821,9 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -821,6 +856,9 @@
       <c r="H12" t="n">
         <v>153</v>
       </c>
+      <c r="I12" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -853,6 +891,9 @@
       <c r="H13" t="n">
         <v>321</v>
       </c>
+      <c r="I13" t="n">
+        <v>321</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -885,6 +926,9 @@
       <c r="H14" t="n">
         <v>147</v>
       </c>
+      <c r="I14" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -917,6 +961,9 @@
       <c r="H15" t="n">
         <v>1634</v>
       </c>
+      <c r="I15" t="n">
+        <v>1634</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -949,6 +996,9 @@
       <c r="H16" t="n">
         <v>176</v>
       </c>
+      <c r="I16" t="n">
+        <v>176</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -981,6 +1031,9 @@
       <c r="H17" t="n">
         <v>605</v>
       </c>
+      <c r="I17" t="n">
+        <v>605</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1013,6 +1066,9 @@
       <c r="H18" t="n">
         <v>429</v>
       </c>
+      <c r="I18" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1045,6 +1101,9 @@
       <c r="H19" t="n">
         <v>343</v>
       </c>
+      <c r="I19" t="n">
+        <v>343</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1077,6 +1136,9 @@
       <c r="H20" t="n">
         <v>362</v>
       </c>
+      <c r="I20" t="n">
+        <v>362</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1109,6 +1171,9 @@
       <c r="H21" t="n">
         <v>266</v>
       </c>
+      <c r="I21" t="n">
+        <v>266</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1139,7 +1204,10 @@
         <v>440</v>
       </c>
       <c r="H22" t="n">
-        <v>440</v>
+        <v>660</v>
+      </c>
+      <c r="I22" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="23">
@@ -1173,6 +1241,9 @@
       <c r="H23" t="n">
         <v>0</v>
       </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1205,6 +1276,9 @@
       <c r="H24" t="n">
         <v>672</v>
       </c>
+      <c r="I24" t="n">
+        <v>672</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1237,6 +1311,9 @@
       <c r="H25" t="n">
         <v>73</v>
       </c>
+      <c r="I25" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1269,6 +1346,9 @@
       <c r="H26" t="n">
         <v>59</v>
       </c>
+      <c r="I26" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1299,7 +1379,10 @@
         <v>385</v>
       </c>
       <c r="H27" t="n">
-        <v>385</v>
+        <v>577.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>577.5</v>
       </c>
     </row>
     <row r="28">
@@ -1331,7 +1414,10 @@
         <v>476</v>
       </c>
       <c r="H28" t="n">
-        <v>476</v>
+        <v>714</v>
+      </c>
+      <c r="I28" t="n">
+        <v>714</v>
       </c>
     </row>
     <row r="29">
@@ -1363,6 +1449,9 @@
         <v>30</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1397,6 +1486,9 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1427,7 +1519,10 @@
         <v>521</v>
       </c>
       <c r="H31" t="n">
-        <v>521</v>
+        <v>781.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>781.5</v>
       </c>
     </row>
     <row r="32">
@@ -1461,6 +1556,9 @@
       <c r="H32" t="n">
         <v>0</v>
       </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1493,6 +1591,9 @@
       <c r="H33" t="n">
         <v>0</v>
       </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1525,6 +1626,9 @@
       <c r="H34" t="n">
         <v>0</v>
       </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1557,6 +1661,9 @@
       <c r="H35" t="n">
         <v>0</v>
       </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1589,6 +1696,9 @@
       <c r="H36" t="n">
         <v>0</v>
       </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1621,6 +1731,9 @@
       <c r="H37" t="n">
         <v>7</v>
       </c>
+      <c r="I37" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1653,6 +1766,9 @@
       <c r="H38" t="n">
         <v>6</v>
       </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1685,6 +1801,9 @@
       <c r="H39" t="n">
         <v>0</v>
       </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1717,6 +1836,9 @@
       <c r="H40" t="n">
         <v>0</v>
       </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1749,6 +1871,9 @@
       <c r="H41" t="n">
         <v>0</v>
       </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1781,6 +1906,9 @@
       <c r="H42" t="n">
         <v>10</v>
       </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1813,6 +1941,9 @@
       <c r="H43" t="n">
         <v>0</v>
       </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1843,6 +1974,9 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/players.xlsx
+++ b/players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_40CDF601567F3A0E62355476585DCE3A8747BDFD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62A674BA-D2A8-4369-B160-6CC35CD797C9}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_40CDF601567F3A0E62355476585DCE3A8747BDFD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64239421-E47A-426A-8EB4-FDCDA413D550}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
   <si>
     <t>Player No</t>
   </si>
@@ -35,18 +35,6 @@
   </si>
   <si>
     <t>starrings</t>
-  </si>
-  <si>
-    <t>July2025_score</t>
-  </si>
-  <si>
-    <t>August2025_score</t>
-  </si>
-  <si>
-    <t>May2025_score</t>
-  </si>
-  <si>
-    <t>June2025_score</t>
   </si>
   <si>
     <t>Ella McMahon</t>
@@ -389,6 +377,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -695,46 +687,26 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>671119</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>2.1</v>
-      </c>
-      <c r="F2">
-        <v>497</v>
-      </c>
-      <c r="G2">
-        <v>497</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -742,28 +714,16 @@
         <v>327350</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>2.1</v>
-      </c>
-      <c r="F3">
-        <v>682</v>
-      </c>
-      <c r="G3">
-        <v>682</v>
-      </c>
-      <c r="H3">
-        <v>682</v>
-      </c>
-      <c r="I3">
-        <v>682</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -771,28 +731,16 @@
         <v>547834</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>2.1</v>
-      </c>
-      <c r="F4">
-        <v>833</v>
-      </c>
-      <c r="G4">
-        <v>833</v>
-      </c>
-      <c r="H4">
-        <v>833</v>
-      </c>
-      <c r="I4">
-        <v>833</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -800,28 +748,16 @@
         <v>74333</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>1.1000000000000001</v>
-      </c>
-      <c r="F5">
-        <v>1314</v>
-      </c>
-      <c r="G5">
-        <v>1314</v>
-      </c>
-      <c r="H5">
-        <v>1971</v>
-      </c>
-      <c r="I5">
-        <v>1971</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -829,28 +765,16 @@
         <v>534286</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>2.2000000000000002</v>
-      </c>
-      <c r="F6">
-        <v>453</v>
-      </c>
-      <c r="G6">
-        <v>453</v>
-      </c>
-      <c r="H6">
-        <v>453</v>
-      </c>
-      <c r="I6">
-        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -858,28 +782,16 @@
         <v>548731</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>2.2000000000000002</v>
-      </c>
-      <c r="F7">
-        <v>339</v>
-      </c>
-      <c r="G7">
-        <v>339</v>
-      </c>
-      <c r="H7">
-        <v>339</v>
-      </c>
-      <c r="I7">
-        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -887,28 +799,16 @@
         <v>110556</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>1.2</v>
-      </c>
-      <c r="F8">
-        <v>643</v>
-      </c>
-      <c r="G8">
-        <v>643</v>
-      </c>
-      <c r="H8">
-        <v>643</v>
-      </c>
-      <c r="I8">
-        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -916,28 +816,16 @@
         <v>662721</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>3.1</v>
-      </c>
-      <c r="F9">
-        <v>516</v>
-      </c>
-      <c r="G9">
-        <v>516</v>
-      </c>
-      <c r="H9">
-        <v>516</v>
-      </c>
-      <c r="I9">
-        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -945,28 +833,16 @@
         <v>3389399</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>1.2</v>
-      </c>
-      <c r="F10">
-        <v>695</v>
-      </c>
-      <c r="G10">
-        <v>695</v>
-      </c>
-      <c r="H10">
-        <v>695</v>
-      </c>
-      <c r="I10">
-        <v>695</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -974,28 +850,16 @@
         <v>74309</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>2.2000000000000002</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1003,28 +867,16 @@
         <v>689814</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>3.1</v>
-      </c>
-      <c r="F12">
-        <v>153</v>
-      </c>
-      <c r="G12">
-        <v>153</v>
-      </c>
-      <c r="H12">
-        <v>153</v>
-      </c>
-      <c r="I12">
-        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1032,28 +884,16 @@
         <v>882252</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>2.2000000000000002</v>
-      </c>
-      <c r="F13">
-        <v>321</v>
-      </c>
-      <c r="G13">
-        <v>321</v>
-      </c>
-      <c r="H13">
-        <v>321</v>
-      </c>
-      <c r="I13">
-        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1061,28 +901,16 @@
         <v>893163</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>3.1</v>
-      </c>
-      <c r="F14">
-        <v>147</v>
-      </c>
-      <c r="G14">
-        <v>147</v>
-      </c>
-      <c r="H14">
-        <v>147</v>
-      </c>
-      <c r="I14">
-        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1090,28 +918,16 @@
         <v>3465549</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E15">
         <v>4</v>
-      </c>
-      <c r="F15">
-        <v>1634</v>
-      </c>
-      <c r="G15">
-        <v>1634</v>
-      </c>
-      <c r="H15">
-        <v>1634</v>
-      </c>
-      <c r="I15">
-        <v>1634</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1119,840 +935,492 @@
         <v>104625</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>1.2</v>
       </c>
-      <c r="F16">
-        <v>176</v>
-      </c>
-      <c r="G16">
-        <v>176</v>
-      </c>
-      <c r="H16">
-        <v>176</v>
-      </c>
-      <c r="I16">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>74263</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E17">
         <v>2.1</v>
       </c>
-      <c r="F17">
-        <v>605</v>
-      </c>
-      <c r="G17">
-        <v>605</v>
-      </c>
-      <c r="H17">
-        <v>605</v>
-      </c>
-      <c r="I17">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>91224</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18">
         <v>1.2</v>
       </c>
-      <c r="F18">
-        <v>429</v>
-      </c>
-      <c r="G18">
-        <v>429</v>
-      </c>
-      <c r="H18">
-        <v>429</v>
-      </c>
-      <c r="I18">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>661554</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E19">
         <v>3.1</v>
       </c>
-      <c r="F19">
-        <v>343</v>
-      </c>
-      <c r="G19">
-        <v>343</v>
-      </c>
-      <c r="H19">
-        <v>343</v>
-      </c>
-      <c r="I19">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>74266</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>2.1</v>
       </c>
-      <c r="F20">
-        <v>362</v>
-      </c>
-      <c r="G20">
-        <v>362</v>
-      </c>
-      <c r="H20">
-        <v>362</v>
-      </c>
-      <c r="I20">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>74331</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E21">
         <v>1.2</v>
       </c>
-      <c r="F21">
-        <v>266</v>
-      </c>
-      <c r="G21">
-        <v>266</v>
-      </c>
-      <c r="H21">
-        <v>266</v>
-      </c>
-      <c r="I21">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>76413</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F22">
-        <v>440</v>
-      </c>
-      <c r="G22">
-        <v>440</v>
-      </c>
-      <c r="H22">
-        <v>660</v>
-      </c>
-      <c r="I22">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>74332</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E23">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>89687</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
-      <c r="F24">
-        <v>672</v>
-      </c>
-      <c r="G24">
-        <v>672</v>
-      </c>
-      <c r="H24">
-        <v>672</v>
-      </c>
-      <c r="I24">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>327209</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E25">
         <v>3.1</v>
       </c>
-      <c r="F25">
-        <v>73</v>
-      </c>
-      <c r="G25">
-        <v>73</v>
-      </c>
-      <c r="H25">
-        <v>73</v>
-      </c>
-      <c r="I25">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>882428</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E26">
         <v>3.2</v>
       </c>
-      <c r="F26">
-        <v>59</v>
-      </c>
-      <c r="G26">
-        <v>59</v>
-      </c>
-      <c r="H26">
-        <v>59</v>
-      </c>
-      <c r="I26">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>76411</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F27">
-        <v>385</v>
-      </c>
-      <c r="G27">
-        <v>385</v>
-      </c>
-      <c r="H27">
-        <v>577.5</v>
-      </c>
-      <c r="I27">
-        <v>577.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>74274</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F28">
-        <v>476</v>
-      </c>
-      <c r="G28">
-        <v>476</v>
-      </c>
-      <c r="H28">
-        <v>714</v>
-      </c>
-      <c r="I28">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>683544</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
-      <c r="F29">
-        <v>30</v>
-      </c>
-      <c r="G29">
-        <v>30</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3281758</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E30">
         <v>4</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>74281</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E31">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F31">
-        <v>521</v>
-      </c>
-      <c r="G31">
-        <v>521</v>
-      </c>
-      <c r="H31">
-        <v>781.5</v>
-      </c>
-      <c r="I31">
-        <v>781.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3276978</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E32">
         <v>4</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>76412</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>687333</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E34">
         <v>4</v>
       </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>326899</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E35">
         <v>3.2</v>
       </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3468653</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E36">
         <v>4</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>75760</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E37">
         <v>2.1</v>
       </c>
-      <c r="F37">
-        <v>7</v>
-      </c>
-      <c r="G37">
-        <v>7</v>
-      </c>
-      <c r="H37">
-        <v>7</v>
-      </c>
-      <c r="I37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>74265</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E38">
         <v>4</v>
       </c>
-      <c r="F38">
-        <v>6</v>
-      </c>
-      <c r="G38">
-        <v>6</v>
-      </c>
-      <c r="H38">
-        <v>6</v>
-      </c>
-      <c r="I38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>554268</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E39">
         <v>4</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3281295</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E40">
         <v>3.2</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>327187</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E41">
         <v>4</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>103786</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E42">
         <v>4</v>
       </c>
-      <c r="F42">
-        <v>10</v>
-      </c>
-      <c r="G42">
-        <v>10</v>
-      </c>
-      <c r="H42">
-        <v>10</v>
-      </c>
-      <c r="I42">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3468321</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E43">
         <v>4</v>
       </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>683019</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E44">
         <v>4</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/players.xlsx
+++ b/players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_40CDF601567F3A0E62355476585DCE3A8747BDFD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64239421-E47A-426A-8EB4-FDCDA413D550}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_40CDF601567F3A0E62355476585DCE3A8747BDFD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E95A718-35A0-40A7-98C8-F211F79C5688}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="114">
   <si>
     <t>Player No</t>
   </si>
@@ -302,13 +302,73 @@
   </si>
   <si>
     <t>https://www2.cricketstatz.com/ss/p/Rachel-Sparrow/?season=2025&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=683019</t>
+  </si>
+  <si>
+    <t>Catherine Nulty</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Catherine-Nulty/?mode=0&amp;playerid=3487968&amp;mininns=&amp;minruns=&amp;minwickets=&amp;minovers=&amp;captains=&amp;club=4537&amp;team=0&amp;season=2026&amp;grade=0&amp;pool=&amp;finals=0&amp;mtype=0</t>
+  </si>
+  <si>
+    <t>Georgina Mullett</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Georgina-Mullett/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3593725</t>
+  </si>
+  <si>
+    <t>Deivanai Alagappan</t>
+  </si>
+  <si>
+    <t>Leinster W4</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Deivanai-Alagappan/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3596369</t>
+  </si>
+  <si>
+    <t>Lara di Nardi</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Lara-Di-Nardi/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3468368</t>
+  </si>
+  <si>
+    <t>Maria Cryan</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Maria-Cryan/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3599115</t>
+  </si>
+  <si>
+    <t>Rachel Kelly</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Rachel-Kelly/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3599490</t>
+  </si>
+  <si>
+    <t>Amanda Simoes</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Amanda-Simoes/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3599116</t>
+  </si>
+  <si>
+    <t>Stephanie Merenbach</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Stephanie-Merenbach/?season=2026&amp;grade=0&amp;pool=&amp;club=4537&amp;playerid=3596368</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Anna-Payet/?mode=0&amp;playerid=3276978&amp;mininns=&amp;minruns=&amp;minwickets=&amp;minovers=&amp;captains=&amp;club=4537&amp;team=0&amp;season=2026&amp;grade=0&amp;pool=&amp;finals=0&amp;mtype=0</t>
+  </si>
+  <si>
+    <t>https://www2.cricketstatz.com/ss/p/Roisin-Hickey/?mode=0&amp;playerid=3469951&amp;mininns=&amp;minruns=&amp;minwickets=&amp;minovers=&amp;captains=&amp;club=4537&amp;team=0&amp;season=2026&amp;grade=0&amp;pool=&amp;finals=0&amp;mtype=0</t>
+  </si>
+  <si>
+    <t>Roisin Hickey</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +380,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -354,16 +422,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -377,10 +448,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1423,7 +1490,159 @@
         <v>4</v>
       </c>
     </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>3487968</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>3593725</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>3596369</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>3468368</v>
+      </c>
+      <c r="B48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>3599115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>3599490</v>
+      </c>
+      <c r="B50" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>3599116</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>3596368</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>3276978</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>3469951</v>
+      </c>
+      <c r="B54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D45" r:id="rId1" xr:uid="{23647257-0515-4B6E-80DB-3F03AF9DC78D}"/>
+    <hyperlink ref="D46" r:id="rId2" xr:uid="{A02CC683-CA11-4CA9-A76F-554D680A47CE}"/>
+    <hyperlink ref="D47" r:id="rId3" xr:uid="{8A89C6FE-E029-4C53-B2F4-FA7D4A05D68A}"/>
+    <hyperlink ref="D48" r:id="rId4" xr:uid="{06595EF7-3991-4FE3-B899-A2BD37C96695}"/>
+    <hyperlink ref="D49" r:id="rId5" xr:uid="{178DB27E-FFDE-42CA-8BDF-D04CF7C7C028}"/>
+    <hyperlink ref="D50" r:id="rId6" xr:uid="{CF3BDD72-1EC0-463A-80B2-F2AFCE1F8B03}"/>
+    <hyperlink ref="D51" r:id="rId7" xr:uid="{63E83B64-F6AA-4951-91D1-200258956112}"/>
+    <hyperlink ref="D52" r:id="rId8" xr:uid="{973F591C-1021-46DF-9E41-1A30DA48535B}"/>
+    <hyperlink ref="D53" r:id="rId9" xr:uid="{4AD98BAC-5AE1-470A-804E-639985C7FDCD}"/>
+    <hyperlink ref="D54" r:id="rId10" xr:uid="{CBBEFC51-7E46-41F8-9F23-7B2B17DBCA84}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>